--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.32890258202139</v>
+        <v>5.415946669578475</v>
       </c>
       <c r="D2" t="n">
-        <v>33.05049587882722</v>
+        <v>5.370705580309424</v>
       </c>
       <c r="E2" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F2" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.86058624484333</v>
+        <v>2.902345264787041</v>
       </c>
       <c r="D3" t="n">
-        <v>17.51842063665803</v>
+        <v>2.84674335345693</v>
       </c>
       <c r="E3" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F3" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.44969991336815</v>
+        <v>4.460576235922324</v>
       </c>
       <c r="D4" t="n">
-        <v>27.27423076961339</v>
+        <v>4.432062500062175</v>
       </c>
       <c r="E4" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F4" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.74452109911375</v>
+        <v>7.758484678605985</v>
       </c>
       <c r="D5" t="n">
-        <v>48.15176638703816</v>
+        <v>7.824662037893701</v>
       </c>
       <c r="E5" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F5" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.30880536187939</v>
+        <v>4.762680871305402</v>
       </c>
       <c r="D6" t="n">
-        <v>29.58837328491881</v>
+        <v>4.808110658799306</v>
       </c>
       <c r="E6" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F6" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.1011451567584</v>
+        <v>5.86643608797324</v>
       </c>
       <c r="D7" t="n">
-        <v>36.61800701360821</v>
+        <v>5.950426139711333</v>
       </c>
       <c r="E7" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F7" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.33687437668551</v>
+        <v>6.717242086211396</v>
       </c>
       <c r="D8" t="n">
-        <v>41.5273838490394</v>
+        <v>6.748199875468902</v>
       </c>
       <c r="E8" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F8" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.32702380315148</v>
+        <v>5.740641368012115</v>
       </c>
       <c r="D9" t="n">
-        <v>35.45548682354799</v>
+        <v>5.761516608826549</v>
       </c>
       <c r="E9" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F9" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.35987827305897</v>
+        <v>5.908480219372084</v>
       </c>
       <c r="D10" t="n">
-        <v>36.69544058332698</v>
+        <v>5.963009094790634</v>
       </c>
       <c r="E10" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F10" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.0339166870034</v>
+        <v>5.205511461638054</v>
       </c>
       <c r="D11" t="n">
-        <v>32.02310902407853</v>
+        <v>5.203755216412762</v>
       </c>
       <c r="E11" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F11" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.06198700849045</v>
+        <v>5.860072888879699</v>
       </c>
       <c r="D12" t="n">
-        <v>36.34518175462843</v>
+        <v>5.90609203512712</v>
       </c>
       <c r="E12" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F12" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.64963713592731</v>
+        <v>6.768066034588188</v>
       </c>
       <c r="D13" t="n">
-        <v>41.45618166331672</v>
+        <v>6.736629520288967</v>
       </c>
       <c r="E13" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F13" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.35318794986885</v>
+        <v>4.282393041853688</v>
       </c>
       <c r="D14" t="n">
-        <v>26.5478556307867</v>
+        <v>4.314026540002838</v>
       </c>
       <c r="E14" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F14" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.04109272675836</v>
+        <v>6.019177568098234</v>
       </c>
       <c r="D15" t="n">
-        <v>36.78389643539133</v>
+        <v>5.977383170751091</v>
       </c>
       <c r="E15" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F15" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.3327522892276</v>
+        <v>6.391572246999485</v>
       </c>
       <c r="D16" t="n">
-        <v>39.42934047327591</v>
+        <v>6.407267826907336</v>
       </c>
       <c r="E16" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F16" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.58958617084287</v>
+        <v>2.695807752761966</v>
       </c>
       <c r="D17" t="n">
-        <v>16.28335099681622</v>
+        <v>2.646044536982636</v>
       </c>
       <c r="E17" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F17" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>31.13256689411606</v>
+        <v>5.059042120293861</v>
       </c>
       <c r="D18" t="n">
-        <v>31.09755429697143</v>
+        <v>5.053352573257858</v>
       </c>
       <c r="E18" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F18" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.74821348646834</v>
+        <v>6.296584691551105</v>
       </c>
       <c r="D19" t="n">
-        <v>38.26276392187916</v>
+        <v>6.217699137305364</v>
       </c>
       <c r="E19" t="n">
-        <v>7.721701452502078</v>
+        <v>1.254776486031588</v>
       </c>
       <c r="F19" t="n">
-        <v>7.835796299203617</v>
+        <v>1.273316898620588</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
